--- a/summer_camps/023_summer_chess_camp_registration_form--summer_camps.xlsx
+++ b/summer_camps/023_summer_chess_camp_registration_form--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Parent Agreement</t>
+          <t>Parent Agreement (2)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>participant_dietary_restrictions</t>
+          <t>participant_dietary_restrictions_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Participant Dietary Restrictions</t>
+          <t>Participant Dietary Restrictions 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>participant_medical_notes</t>
+          <t>participant_medical_notes_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Participant Medical Notes</t>
+          <t>Participant Medical Notes 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>payment_status_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Payment Status</t>
+          <t>Payment Status 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>payment_status_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1615,7 +1615,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>payment_status_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
